--- a/mfd_de_referenz.xlsx
+++ b/mfd_de_referenz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/finn.recktenwald/Library/CloudStorage/OneDrive-adessoGroup/Dokumente/Privat/Master Kognitionswissenschaft/Praktikum/Pilot/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/finn.recktenwald/VS Code/Moral Prompting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{241FDF14-9678-1449-BD89-951FC9F58B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE65891-5037-C841-9A2A-3F32A2220698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="19000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="1231">
   <si>
     <t>term</t>
   </si>
@@ -59,12 +59,6 @@
     <t>prefix</t>
   </si>
   <si>
-    <t>abhaenhigkeit</t>
-  </si>
-  <si>
-    <t>abhaenhigkeit*</t>
-  </si>
-  <si>
     <t>abkehren</t>
   </si>
   <si>
@@ -290,12 +284,6 @@
     <t>aufopfer*</t>
   </si>
   <si>
-    <t>aufrichig</t>
-  </si>
-  <si>
-    <t>aufrichig*</t>
-  </si>
-  <si>
     <t>aufrichtig</t>
   </si>
   <si>
@@ -920,12 +908,6 @@
     <t>ekel*</t>
   </si>
   <si>
-    <t>ekelerreged</t>
-  </si>
-  <si>
-    <t>ekelerreged*</t>
-  </si>
-  <si>
     <t>elend</t>
   </si>
   <si>
@@ -1040,12 +1022,6 @@
     <t>erhaltung*</t>
   </si>
   <si>
-    <t>erhbietung</t>
-  </si>
-  <si>
-    <t>erhbietung*</t>
-  </si>
-  <si>
     <t>erkrankt</t>
   </si>
   <si>
@@ -1340,12 +1316,6 @@
     <t>gegner*</t>
   </si>
   <si>
-    <t>gehnemigung</t>
-  </si>
-  <si>
-    <t>gehnemigung*</t>
-  </si>
-  <si>
     <t>gehorchen</t>
   </si>
   <si>
@@ -1376,12 +1346,6 @@
     <t>gemein*</t>
   </si>
   <si>
-    <t>genhemigen</t>
-  </si>
-  <si>
-    <t>genhemigen*</t>
-  </si>
-  <si>
     <t>genoss</t>
   </si>
   <si>
@@ -3723,6 +3687,36 @@
   </si>
   <si>
     <t>09 | 10</t>
+  </si>
+  <si>
+    <t>abhaengigkeit</t>
+  </si>
+  <si>
+    <t>abhaengigkeit*</t>
+  </si>
+  <si>
+    <t>ekelerregend</t>
+  </si>
+  <si>
+    <t>ekelerregend*</t>
+  </si>
+  <si>
+    <t>ehrbietung</t>
+  </si>
+  <si>
+    <t>ehrbietung*</t>
+  </si>
+  <si>
+    <t>genehmigung</t>
+  </si>
+  <si>
+    <t>genehmigung*</t>
+  </si>
+  <si>
+    <t>genehmigen</t>
+  </si>
+  <si>
+    <t>genehmigen*</t>
   </si>
 </sst>
 </file>
@@ -4228,10 +4222,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>1221</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>1222</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -4254,10 +4248,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
@@ -4280,10 +4274,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>10</v>
@@ -4306,10 +4300,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -4332,10 +4326,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -4358,10 +4352,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -4384,13 +4378,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" s="11">
         <v>0</v>
@@ -4410,10 +4404,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>10</v>
@@ -4436,10 +4430,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>10</v>
@@ -4462,10 +4456,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>10</v>
@@ -4488,10 +4482,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>10</v>
@@ -4514,10 +4508,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>10</v>
@@ -4540,10 +4534,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>10</v>
@@ -4566,10 +4560,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>10</v>
@@ -4592,10 +4586,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>10</v>
@@ -4618,10 +4612,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>10</v>
@@ -4644,10 +4638,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>10</v>
@@ -4670,10 +4664,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>10</v>
@@ -4696,10 +4690,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>10</v>
@@ -4722,10 +4716,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>10</v>
@@ -4748,10 +4742,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>10</v>
@@ -4774,10 +4768,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>10</v>
@@ -4800,10 +4794,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>10</v>
@@ -4826,10 +4820,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
@@ -4852,10 +4846,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>10</v>
@@ -4878,10 +4872,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>10</v>
@@ -4904,10 +4898,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>10</v>
@@ -4930,13 +4924,13 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D30" s="11">
         <v>0</v>
@@ -4956,10 +4950,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>10</v>
@@ -4982,10 +4976,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>10</v>
@@ -5008,10 +5002,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>10</v>
@@ -5034,10 +5028,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>10</v>
@@ -5060,10 +5054,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>10</v>
@@ -5086,10 +5080,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
@@ -5112,10 +5106,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>10</v>
@@ -5138,10 +5132,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>10</v>
@@ -5164,10 +5158,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>10</v>
@@ -5190,10 +5184,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>10</v>
@@ -5216,10 +5210,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>10</v>
@@ -5242,10 +5236,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>10</v>
@@ -5268,10 +5262,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>10</v>
@@ -5294,10 +5288,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>10</v>
@@ -5320,10 +5314,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>10</v>
@@ -5346,10 +5340,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>10</v>
@@ -5372,10 +5366,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>10</v>
@@ -5398,10 +5392,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>10</v>
@@ -5424,10 +5418,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>10</v>
@@ -5450,10 +5444,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>10</v>
@@ -5476,10 +5470,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>10</v>
@@ -5502,10 +5496,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>10</v>
@@ -5528,10 +5522,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
@@ -5554,10 +5548,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>10</v>
@@ -5580,10 +5574,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>10</v>
@@ -5606,10 +5600,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>10</v>
@@ -5632,10 +5626,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>10</v>
@@ -5658,10 +5652,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>10</v>
@@ -5684,10 +5678,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>10</v>
@@ -5710,10 +5704,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>10</v>
@@ -5736,10 +5730,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>10</v>
@@ -5762,10 +5756,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
@@ -5788,10 +5782,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -5814,10 +5808,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>10</v>
@@ -5840,10 +5834,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>10</v>
@@ -5866,10 +5860,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>10</v>
@@ -5892,10 +5886,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>10</v>
@@ -5918,10 +5912,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>10</v>
@@ -5944,10 +5938,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>10</v>
@@ -5970,10 +5964,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>10</v>
@@ -5996,10 +5990,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>10</v>
@@ -6022,10 +6016,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>10</v>
@@ -6048,10 +6042,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>10</v>
@@ -6074,10 +6068,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>10</v>
@@ -6100,10 +6094,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>10</v>
@@ -6126,10 +6120,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>10</v>
@@ -6152,10 +6146,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>10</v>
@@ -6178,10 +6172,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>10</v>
@@ -6204,10 +6198,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>10</v>
@@ -6230,10 +6224,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>10</v>
@@ -6256,13 +6250,13 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D81" s="9">
         <v>0</v>
@@ -6282,10 +6276,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>10</v>
@@ -6308,10 +6302,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>10</v>
@@ -6334,13 +6328,13 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D84" s="3">
         <v>1</v>
@@ -6360,10 +6354,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>10</v>
@@ -6386,10 +6380,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>10</v>
@@ -6412,10 +6406,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>10</v>
@@ -6438,10 +6432,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>10</v>
@@ -6464,10 +6458,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
@@ -6490,10 +6484,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>10</v>
@@ -6516,10 +6510,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>10</v>
@@ -6542,10 +6536,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>10</v>
@@ -6568,10 +6562,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>10</v>
@@ -6594,10 +6588,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>10</v>
@@ -6620,10 +6614,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>10</v>
@@ -6646,10 +6640,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>10</v>
@@ -6672,10 +6666,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>10</v>
@@ -6698,10 +6692,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>10</v>
@@ -6724,10 +6718,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>10</v>
@@ -6750,10 +6744,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>10</v>
@@ -6776,10 +6770,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>10</v>
@@ -6802,10 +6796,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>10</v>
@@ -6828,10 +6822,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>10</v>
@@ -6854,10 +6848,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>10</v>
@@ -6880,10 +6874,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>10</v>
@@ -6906,10 +6900,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>10</v>
@@ -6932,10 +6926,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>10</v>
@@ -6958,10 +6952,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>10</v>
@@ -6984,10 +6978,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>10</v>
@@ -7010,10 +7004,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>10</v>
@@ -7036,10 +7030,10 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>10</v>
@@ -7062,10 +7056,10 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>10</v>
@@ -7088,10 +7082,10 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>10</v>
@@ -7114,10 +7108,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>10</v>
@@ -7140,10 +7134,10 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>10</v>
@@ -7166,10 +7160,10 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>10</v>
@@ -7192,10 +7186,10 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>10</v>
@@ -7218,10 +7212,10 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>10</v>
@@ -7244,10 +7238,10 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>10</v>
@@ -7270,10 +7264,10 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>10</v>
@@ -7296,10 +7290,10 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>10</v>
@@ -7322,13 +7316,13 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D122" s="9">
         <v>0</v>
@@ -7348,10 +7342,10 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>10</v>
@@ -7374,10 +7368,10 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>10</v>
@@ -7400,10 +7394,10 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>10</v>
@@ -7426,10 +7420,10 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>10</v>
@@ -7452,10 +7446,10 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>10</v>
@@ -7478,10 +7472,10 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>10</v>
@@ -7504,10 +7498,10 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>10</v>
@@ -7530,10 +7524,10 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>10</v>
@@ -7556,10 +7550,10 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="12" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>10</v>
@@ -7582,10 +7576,10 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="12" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>10</v>
@@ -7608,10 +7602,10 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="10" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>10</v>
@@ -7634,10 +7628,10 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="12" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>10</v>
@@ -7660,10 +7654,10 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>10</v>
@@ -7686,13 +7680,13 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D136" s="11">
         <v>0</v>
@@ -7712,10 +7706,10 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>10</v>
@@ -7738,10 +7732,10 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="12" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>10</v>
@@ -7764,10 +7758,10 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>10</v>
@@ -7790,10 +7784,10 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>10</v>
@@ -7816,10 +7810,10 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>10</v>
@@ -7842,10 +7836,10 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>10</v>
@@ -7868,13 +7862,13 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D143" s="9">
         <v>0</v>
@@ -7894,10 +7888,10 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>10</v>
@@ -7920,10 +7914,10 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>10</v>
@@ -7946,10 +7940,10 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>10</v>
@@ -7972,10 +7966,10 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>10</v>
@@ -7998,13 +7992,13 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D148" s="9">
         <v>0</v>
@@ -8024,10 +8018,10 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="10" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>10</v>
@@ -8050,10 +8044,10 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="10" t="s">
-        <v>298</v>
+        <v>1223</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>299</v>
+        <v>1224</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>10</v>
@@ -8076,10 +8070,10 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>10</v>
@@ -8102,10 +8096,10 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>10</v>
@@ -8128,10 +8122,10 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="10" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>10</v>
@@ -8154,10 +8148,10 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="10" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>10</v>
@@ -8180,10 +8174,10 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>10</v>
@@ -8206,10 +8200,10 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>10</v>
@@ -8232,10 +8226,10 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>10</v>
@@ -8258,10 +8252,10 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>10</v>
@@ -8284,10 +8278,10 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="10" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>10</v>
@@ -8310,10 +8304,10 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="12" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C160" s="12" t="s">
         <v>10</v>
@@ -8336,10 +8330,10 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="10" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>10</v>
@@ -8362,10 +8356,10 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>10</v>
@@ -8388,10 +8382,10 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>10</v>
@@ -8414,10 +8408,10 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>10</v>
@@ -8440,10 +8434,10 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>10</v>
@@ -8466,10 +8460,10 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>10</v>
@@ -8492,10 +8486,10 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="6" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>10</v>
@@ -8518,10 +8512,10 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="6" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>10</v>
@@ -8544,10 +8538,10 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>10</v>
@@ -8570,10 +8564,10 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>338</v>
+        <v>1225</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>339</v>
+        <v>1226</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>10</v>
@@ -8596,10 +8590,10 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="10" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>10</v>
@@ -8622,10 +8616,10 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>10</v>
@@ -8648,10 +8642,10 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>10</v>
@@ -8674,10 +8668,10 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>10</v>
@@ -8700,10 +8694,10 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>10</v>
@@ -8726,10 +8720,10 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>10</v>
@@ -8752,10 +8746,10 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>10</v>
@@ -8778,10 +8772,10 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>10</v>
@@ -8804,10 +8798,10 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>10</v>
@@ -8830,10 +8824,10 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="10" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>10</v>
@@ -8856,10 +8850,10 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>10</v>
@@ -8882,10 +8876,10 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>10</v>
@@ -8908,10 +8902,10 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>10</v>
@@ -8934,10 +8928,10 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="12" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>10</v>
@@ -8960,10 +8954,10 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="10" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>10</v>
@@ -8986,10 +8980,10 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="6" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>10</v>
@@ -9012,10 +9006,10 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="12" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>10</v>
@@ -9038,10 +9032,10 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>10</v>
@@ -9064,10 +9058,10 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>10</v>
@@ -9090,10 +9084,10 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>10</v>
@@ -9116,10 +9110,10 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="12" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>10</v>
@@ -9142,10 +9136,10 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="12" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>10</v>
@@ -9168,10 +9162,10 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="10" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C193" s="10" t="s">
         <v>10</v>
@@ -9194,10 +9188,10 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="10" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C194" s="10" t="s">
         <v>10</v>
@@ -9220,10 +9214,10 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>10</v>
@@ -9246,13 +9240,13 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="10" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D196" s="11">
         <v>0</v>
@@ -9272,10 +9266,10 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>10</v>
@@ -9298,10 +9292,10 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>10</v>
@@ -9324,10 +9318,10 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>10</v>
@@ -9350,10 +9344,10 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>10</v>
@@ -9376,10 +9370,10 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="8" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>10</v>
@@ -9402,13 +9396,13 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D202" s="3">
         <v>1</v>
@@ -9428,10 +9422,10 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>10</v>
@@ -9454,10 +9448,10 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>10</v>
@@ -9480,13 +9474,13 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D205" s="7">
         <v>0</v>
@@ -9506,10 +9500,10 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>10</v>
@@ -9532,10 +9526,10 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>10</v>
@@ -9558,10 +9552,10 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
@@ -9584,10 +9578,10 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>10</v>
@@ -9610,10 +9604,10 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>10</v>
@@ -9636,13 +9630,13 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="10" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D211" s="11">
         <v>0</v>
@@ -9662,10 +9656,10 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="8" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>10</v>
@@ -9688,10 +9682,10 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -9714,10 +9708,10 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>10</v>
@@ -9740,10 +9734,10 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>10</v>
@@ -9766,10 +9760,10 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="10" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C216" s="10" t="s">
         <v>10</v>
@@ -9792,10 +9786,10 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>10</v>
@@ -9818,10 +9812,10 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>10</v>
@@ -9844,10 +9838,10 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="12" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>10</v>
@@ -9870,10 +9864,10 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -9896,10 +9890,10 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C221" s="8" t="s">
         <v>10</v>
@@ -9922,10 +9916,10 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
-        <v>438</v>
+        <v>1227</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>439</v>
+        <v>1228</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>10</v>
@@ -9948,10 +9942,10 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>10</v>
@@ -9974,10 +9968,10 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>10</v>
@@ -10000,10 +9994,10 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="10" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C225" s="10" t="s">
         <v>10</v>
@@ -10026,10 +10020,10 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="10" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C226" s="10" t="s">
         <v>10</v>
@@ -10052,10 +10046,10 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="6" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>10</v>
@@ -10078,10 +10072,10 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
-        <v>450</v>
+        <v>1229</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>451</v>
+        <v>1230</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>10</v>
@@ -10104,10 +10098,10 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="8" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>10</v>
@@ -10130,10 +10124,10 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="6" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>10</v>
@@ -10156,10 +10150,10 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="6" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>10</v>
@@ -10182,10 +10176,10 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="10" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C232" s="10" t="s">
         <v>10</v>
@@ -10208,10 +10202,10 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>10</v>
@@ -10234,10 +10228,10 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="6" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>10</v>
@@ -10260,10 +10254,10 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="6" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>10</v>
@@ -10286,10 +10280,10 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>10</v>
@@ -10312,10 +10306,10 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="6" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>10</v>
@@ -10338,10 +10332,10 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="6" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>10</v>
@@ -10364,10 +10358,10 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>10</v>
@@ -10390,10 +10384,10 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>10</v>
@@ -10416,10 +10410,10 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="12" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B241" s="12" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C241" s="12" t="s">
         <v>10</v>
@@ -10442,13 +10436,13 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="8" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D242" s="9">
         <v>0</v>
@@ -10468,10 +10462,10 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="6" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>10</v>
@@ -10494,10 +10488,10 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="10" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C244" s="10" t="s">
         <v>10</v>
@@ -10520,10 +10514,10 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>10</v>
@@ -10546,10 +10540,10 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>10</v>
@@ -10572,10 +10566,10 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="10" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C247" s="10" t="s">
         <v>10</v>
@@ -10598,10 +10592,10 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C248" s="8" t="s">
         <v>10</v>
@@ -10624,10 +10618,10 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C249" s="8" t="s">
         <v>10</v>
@@ -10650,10 +10644,10 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>10</v>
@@ -10676,10 +10670,10 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="6" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C251" s="6" t="s">
         <v>10</v>
@@ -10702,10 +10696,10 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="10" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>10</v>
@@ -10728,10 +10722,10 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="10" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>10</v>
@@ -10754,10 +10748,10 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="8" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C254" s="8" t="s">
         <v>10</v>
@@ -10780,10 +10774,10 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="6" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C255" s="6" t="s">
         <v>10</v>
@@ -10806,10 +10800,10 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="8" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C256" s="8" t="s">
         <v>10</v>
@@ -10832,10 +10826,10 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>10</v>
@@ -10858,10 +10852,10 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="8" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C258" s="8" t="s">
         <v>10</v>
@@ -10884,10 +10878,10 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="10" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C259" s="10" t="s">
         <v>10</v>
@@ -10910,10 +10904,10 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="10" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C260" s="10" t="s">
         <v>10</v>
@@ -10936,10 +10930,10 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="10" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C261" s="10" t="s">
         <v>10</v>
@@ -10962,10 +10956,10 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>10</v>
@@ -10988,10 +10982,10 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>10</v>
@@ -11014,10 +11008,10 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>10</v>
@@ -11040,10 +11034,10 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>10</v>
@@ -11066,10 +11060,10 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>10</v>
@@ -11092,10 +11086,10 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>10</v>
@@ -11118,10 +11112,10 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="8" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C268" s="8" t="s">
         <v>10</v>
@@ -11144,10 +11138,10 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="8" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="C269" s="8" t="s">
         <v>10</v>
@@ -11170,10 +11164,10 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="8" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>10</v>
@@ -11196,10 +11190,10 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="8" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C271" s="8" t="s">
         <v>10</v>
@@ -11222,10 +11216,10 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="6" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C272" s="6" t="s">
         <v>10</v>
@@ -11248,10 +11242,10 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="10" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C273" s="10" t="s">
         <v>10</v>
@@ -11274,10 +11268,10 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>10</v>
@@ -11300,10 +11294,10 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>10</v>
@@ -11326,13 +11320,13 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="8" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D276" s="9">
         <v>0</v>
@@ -11352,10 +11346,10 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="8" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>10</v>
@@ -11378,13 +11372,13 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="8" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D278" s="9">
         <v>0</v>
@@ -11404,10 +11398,10 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="10" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C279" s="10" t="s">
         <v>10</v>
@@ -11430,10 +11424,10 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="12" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C280" s="12" t="s">
         <v>10</v>
@@ -11456,10 +11450,10 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="8" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C281" s="8" t="s">
         <v>10</v>
@@ -11482,10 +11476,10 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="10" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="C282" s="10" t="s">
         <v>10</v>
@@ -11508,10 +11502,10 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="6" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C283" s="6" t="s">
         <v>10</v>
@@ -11534,13 +11528,13 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="10" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D284" s="11">
         <v>0</v>
@@ -11560,10 +11554,10 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="10" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="C285" s="10" t="s">
         <v>10</v>
@@ -11586,10 +11580,10 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="12" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B286" s="12" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C286" s="12" t="s">
         <v>10</v>
@@ -11612,13 +11606,13 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="8" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D287" s="9">
         <v>0</v>
@@ -11638,10 +11632,10 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>10</v>
@@ -11664,10 +11658,10 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="8" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C289" s="8" t="s">
         <v>10</v>
@@ -11690,13 +11684,13 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D290" s="3">
         <v>1</v>
@@ -11716,10 +11710,10 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="8" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C291" s="8" t="s">
         <v>10</v>
@@ -11742,10 +11736,10 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="10" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C292" s="10" t="s">
         <v>10</v>
@@ -11768,10 +11762,10 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>10</v>
@@ -11794,10 +11788,10 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="10" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C294" s="10" t="s">
         <v>10</v>
@@ -11820,10 +11814,10 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>10</v>
@@ -11846,10 +11840,10 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>10</v>
@@ -11872,10 +11866,10 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="10" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C297" s="10" t="s">
         <v>10</v>
@@ -11898,10 +11892,10 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="10" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="C298" s="10" t="s">
         <v>10</v>
@@ -11924,10 +11918,10 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="10" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="C299" s="10" t="s">
         <v>10</v>
@@ -11950,10 +11944,10 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>10</v>
@@ -11976,13 +11970,13 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="8" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="B301" s="8" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D301" s="9">
         <v>0</v>
@@ -12002,10 +11996,10 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="8" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C302" s="8" t="s">
         <v>10</v>
@@ -12028,10 +12022,10 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="8" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C303" s="8" t="s">
         <v>10</v>
@@ -12054,10 +12048,10 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>10</v>
@@ -12080,10 +12074,10 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>10</v>
@@ -12106,10 +12100,10 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="8" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C306" s="8" t="s">
         <v>10</v>
@@ -12132,10 +12126,10 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="10" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C307" s="10" t="s">
         <v>10</v>
@@ -12158,10 +12152,10 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>10</v>
@@ -12184,10 +12178,10 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>10</v>
@@ -12210,10 +12204,10 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="12" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B310" s="12" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C310" s="12" t="s">
         <v>10</v>
@@ -12236,10 +12230,10 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>10</v>
@@ -12262,10 +12256,10 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="10" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C312" s="10" t="s">
         <v>10</v>
@@ -12288,10 +12282,10 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>10</v>
@@ -12314,10 +12308,10 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>10</v>
@@ -12340,10 +12334,10 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="10" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>10</v>
@@ -12366,10 +12360,10 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="10" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C316" s="10" t="s">
         <v>10</v>
@@ -12392,10 +12386,10 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="10" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C317" s="10" t="s">
         <v>10</v>
@@ -12418,10 +12412,10 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="6" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C318" s="6" t="s">
         <v>10</v>
@@ -12444,10 +12438,10 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>10</v>
@@ -12470,10 +12464,10 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>10</v>
@@ -12496,10 +12490,10 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>10</v>
@@ -12522,13 +12516,13 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D322" s="3">
         <v>1</v>
@@ -12548,10 +12542,10 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>10</v>
@@ -12574,10 +12568,10 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="10" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C324" s="10" t="s">
         <v>10</v>
@@ -12600,10 +12594,10 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="10" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>10</v>
@@ -12626,10 +12620,10 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="8" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="C326" s="8" t="s">
         <v>10</v>
@@ -12652,10 +12646,10 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="8" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C327" s="8" t="s">
         <v>10</v>
@@ -12678,10 +12672,10 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="10" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="C328" s="10" t="s">
         <v>10</v>
@@ -12704,10 +12698,10 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="10" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="C329" s="10" t="s">
         <v>10</v>
@@ -12730,10 +12724,10 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="10" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="B330" s="10" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C330" s="10" t="s">
         <v>10</v>
@@ -12756,10 +12750,10 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="10" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C331" s="10" t="s">
         <v>10</v>
@@ -12782,10 +12776,10 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="10" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="C332" s="10" t="s">
         <v>10</v>
@@ -12808,10 +12802,10 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="10" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="C333" s="10" t="s">
         <v>10</v>
@@ -12834,10 +12828,10 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>10</v>
@@ -12860,10 +12854,10 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="10" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C335" s="10" t="s">
         <v>10</v>
@@ -12886,10 +12880,10 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="6" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="C336" s="6" t="s">
         <v>10</v>
@@ -12912,10 +12906,10 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>10</v>
@@ -12938,10 +12932,10 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="6" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="C338" s="6" t="s">
         <v>10</v>
@@ -12964,10 +12958,10 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>10</v>
@@ -12990,10 +12984,10 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>10</v>
@@ -13016,13 +13010,13 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="8" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C341" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D341" s="9">
         <v>0</v>
@@ -13042,13 +13036,13 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="8" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="C342" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D342" s="9">
         <v>0</v>
@@ -13068,10 +13062,10 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>10</v>
@@ -13094,10 +13088,10 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="8" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="C344" s="8" t="s">
         <v>10</v>
@@ -13120,10 +13114,10 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>10</v>
@@ -13146,10 +13140,10 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>10</v>
@@ -13172,13 +13166,13 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="4" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D347" s="5">
         <v>0</v>
@@ -13198,10 +13192,10 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>10</v>
@@ -13224,10 +13218,10 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="4" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>10</v>
@@ -13250,10 +13244,10 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="10" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="C350" s="10" t="s">
         <v>10</v>
@@ -13276,10 +13270,10 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="6" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="C351" s="6" t="s">
         <v>10</v>
@@ -13302,10 +13296,10 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="10" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="C352" s="10" t="s">
         <v>10</v>
@@ -13328,10 +13322,10 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="8" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="C353" s="8" t="s">
         <v>10</v>
@@ -13354,10 +13348,10 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>10</v>
@@ -13380,10 +13374,10 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>10</v>
@@ -13406,10 +13400,10 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="12" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="B356" s="12" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="C356" s="12" t="s">
         <v>10</v>
@@ -13432,10 +13426,10 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="10" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="C357" s="10" t="s">
         <v>10</v>
@@ -13458,10 +13452,10 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="4" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>10</v>
@@ -13484,10 +13478,10 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="10" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="C359" s="10" t="s">
         <v>10</v>
@@ -13510,10 +13504,10 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="10" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="C360" s="10" t="s">
         <v>10</v>
@@ -13536,10 +13530,10 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>10</v>
@@ -13562,13 +13556,13 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D362" s="3">
         <v>1</v>
@@ -13588,10 +13582,10 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="4" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>10</v>
@@ -13614,10 +13608,10 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="10" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="C364" s="10" t="s">
         <v>10</v>
@@ -13640,10 +13634,10 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="8" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="B365" s="8" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="C365" s="8" t="s">
         <v>10</v>
@@ -13666,10 +13660,10 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="4" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>10</v>
@@ -13692,10 +13686,10 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="6" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="C367" s="6" t="s">
         <v>10</v>
@@ -13718,10 +13712,10 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="12" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="B368" s="12" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C368" s="12" t="s">
         <v>10</v>
@@ -13744,10 +13738,10 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="10" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="C369" s="10" t="s">
         <v>10</v>
@@ -13770,10 +13764,10 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="4" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>10</v>
@@ -13796,10 +13790,10 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="8" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B371" s="8" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C371" s="8" t="s">
         <v>10</v>
@@ -13822,10 +13816,10 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="8" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="C372" s="8" t="s">
         <v>10</v>
@@ -13848,10 +13842,10 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="6" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="C373" s="6" t="s">
         <v>10</v>
@@ -13874,10 +13868,10 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="10" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="C374" s="10" t="s">
         <v>10</v>
@@ -13900,10 +13894,10 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="4" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>10</v>
@@ -13926,10 +13920,10 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="10" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="B376" s="10" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="C376" s="10" t="s">
         <v>10</v>
@@ -13952,10 +13946,10 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="4" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>10</v>
@@ -13978,10 +13972,10 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="6" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="C378" s="6" t="s">
         <v>10</v>
@@ -14004,10 +13998,10 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="10" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="B379" s="10" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="C379" s="10" t="s">
         <v>10</v>
@@ -14030,10 +14024,10 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="10" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="B380" s="10" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="C380" s="10" t="s">
         <v>10</v>
@@ -14056,10 +14050,10 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="10" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="B381" s="10" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="C381" s="10" t="s">
         <v>10</v>
@@ -14082,10 +14076,10 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="4" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>10</v>
@@ -14108,10 +14102,10 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="2" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>10</v>
@@ -14134,10 +14128,10 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="10" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="B384" s="10" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="C384" s="10" t="s">
         <v>10</v>
@@ -14160,10 +14154,10 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="4" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>10</v>
@@ -14186,10 +14180,10 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="4" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>10</v>
@@ -14212,10 +14206,10 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="4" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>10</v>
@@ -14238,13 +14232,13 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="4" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D388" s="5">
         <v>0</v>
@@ -14264,10 +14258,10 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="2" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>10</v>
@@ -14290,10 +14284,10 @@
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="4" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>10</v>
@@ -14316,10 +14310,10 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="6" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="C391" s="6" t="s">
         <v>10</v>
@@ -14342,10 +14336,10 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="10" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="C392" s="10" t="s">
         <v>10</v>
@@ -14368,10 +14362,10 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="4" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>10</v>
@@ -14394,10 +14388,10 @@
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="10" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="C394" s="10" t="s">
         <v>10</v>
@@ -14420,13 +14414,13 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="4" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D395" s="5">
         <v>0</v>
@@ -14446,10 +14440,10 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="4" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>10</v>
@@ -14472,10 +14466,10 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="4" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>10</v>
@@ -14498,10 +14492,10 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="4" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>10</v>
@@ -14524,10 +14518,10 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="4" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>10</v>
@@ -14550,10 +14544,10 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="4" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>10</v>
@@ -14576,10 +14570,10 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>10</v>
@@ -14602,10 +14596,10 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="2" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>10</v>
@@ -14628,10 +14622,10 @@
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="10" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="B403" s="10" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="C403" s="10" t="s">
         <v>10</v>
@@ -14654,10 +14648,10 @@
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="6" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="C404" s="6" t="s">
         <v>10</v>
@@ -14680,10 +14674,10 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>10</v>
@@ -14706,10 +14700,10 @@
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="2" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>10</v>
@@ -14732,10 +14726,10 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="10" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="C407" s="10" t="s">
         <v>10</v>
@@ -14758,10 +14752,10 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="10" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="C408" s="10" t="s">
         <v>10</v>
@@ -14784,10 +14778,10 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="6" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="C409" s="6" t="s">
         <v>10</v>
@@ -14810,10 +14804,10 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="10" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="C410" s="10" t="s">
         <v>10</v>
@@ -14836,13 +14830,13 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="10" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D411" s="11">
         <v>0</v>
@@ -14862,10 +14856,10 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" s="10" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="C412" s="10" t="s">
         <v>10</v>
@@ -14888,10 +14882,10 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" s="8" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="C413" s="8" t="s">
         <v>10</v>
@@ -14914,10 +14908,10 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="6" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="C414" s="6" t="s">
         <v>10</v>
@@ -14940,10 +14934,10 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>10</v>
@@ -14966,13 +14960,13 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="2" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D416" s="3">
         <v>1</v>
@@ -14992,10 +14986,10 @@
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="10" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="C417" s="10" t="s">
         <v>10</v>
@@ -15018,10 +15012,10 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="10" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C418" s="10" t="s">
         <v>10</v>
@@ -15044,10 +15038,10 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="10" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="C419" s="10" t="s">
         <v>10</v>
@@ -15070,10 +15064,10 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="6" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="C420" s="6" t="s">
         <v>10</v>
@@ -15096,10 +15090,10 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="10" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="C421" s="10" t="s">
         <v>10</v>
@@ -15122,10 +15116,10 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="2" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>10</v>
@@ -15148,10 +15142,10 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="10" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>10</v>
@@ -15174,10 +15168,10 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="10" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="C424" s="10" t="s">
         <v>10</v>
@@ -15200,10 +15194,10 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="10" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="C425" s="10" t="s">
         <v>10</v>
@@ -15226,13 +15220,13 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="10" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="B426" s="10" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D426" s="11">
         <v>0</v>
@@ -15252,10 +15246,10 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>10</v>
@@ -15278,10 +15272,10 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>10</v>
@@ -15304,10 +15298,10 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="6" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="C429" s="6" t="s">
         <v>10</v>
@@ -15330,10 +15324,10 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="10" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="C430" s="10" t="s">
         <v>10</v>
@@ -15356,10 +15350,10 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="8" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
       <c r="C431" s="8" t="s">
         <v>10</v>
@@ -15382,10 +15376,10 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>10</v>
@@ -15408,10 +15402,10 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" s="10" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="B433" s="10" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="C433" s="10" t="s">
         <v>10</v>
@@ -15434,10 +15428,10 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" s="8" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="C434" s="8" t="s">
         <v>10</v>
@@ -15460,10 +15454,10 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" s="10" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="B435" s="10" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="C435" s="10" t="s">
         <v>10</v>
@@ -15486,10 +15480,10 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" s="12" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="B436" s="12" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="C436" s="12" t="s">
         <v>10</v>
@@ -15512,10 +15506,10 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>10</v>
@@ -15538,10 +15532,10 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="10" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="B438" s="10" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="C438" s="10" t="s">
         <v>10</v>
@@ -15564,10 +15558,10 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" s="8" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="C439" s="8" t="s">
         <v>10</v>
@@ -15590,10 +15584,10 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="10" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="B440" s="10" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="C440" s="10" t="s">
         <v>10</v>
@@ -15616,10 +15610,10 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="12" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B441" s="12" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="C441" s="12" t="s">
         <v>10</v>
@@ -15642,10 +15636,10 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" s="8" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="B442" s="8" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="C442" s="8" t="s">
         <v>10</v>
@@ -15668,10 +15662,10 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>10</v>
@@ -15694,10 +15688,10 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>10</v>
@@ -15720,10 +15714,10 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" s="12" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="B445" s="12" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="C445" s="12" t="s">
         <v>10</v>
@@ -15746,10 +15740,10 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>10</v>
@@ -15772,10 +15766,10 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" s="8" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="B447" s="8" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="C447" s="8" t="s">
         <v>10</v>
@@ -15798,10 +15792,10 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" s="8" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="B448" s="8" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="C448" s="8" t="s">
         <v>10</v>
@@ -15824,10 +15818,10 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" s="4" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>10</v>
@@ -15850,10 +15844,10 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>10</v>
@@ -15876,10 +15870,10 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" s="4" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>10</v>
@@ -15902,10 +15896,10 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" s="10" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="B452" s="10" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="C452" s="10" t="s">
         <v>10</v>
@@ -15928,10 +15922,10 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>10</v>
@@ -15954,13 +15948,13 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" s="10" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="B454" s="10" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="C454" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D454" s="11">
         <v>0</v>
@@ -15980,10 +15974,10 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" s="10" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="B455" s="10" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="C455" s="10" t="s">
         <v>10</v>
@@ -16006,13 +16000,13 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" s="4" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D456" s="5">
         <v>0</v>
@@ -16032,10 +16026,10 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" s="10" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="B457" s="10" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="C457" s="10" t="s">
         <v>10</v>
@@ -16058,10 +16052,10 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" s="4" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>10</v>
@@ -16084,13 +16078,13 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" s="10" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="B459" s="10" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D459" s="11">
         <v>0</v>
@@ -16110,10 +16104,10 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" s="10" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="B460" s="10" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="C460" s="10" t="s">
         <v>10</v>
@@ -16136,10 +16130,10 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" s="8" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="B461" s="8" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="C461" s="8" t="s">
         <v>10</v>
@@ -16162,10 +16156,10 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" s="6" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="B462" s="6" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="C462" s="6" t="s">
         <v>10</v>
@@ -16188,10 +16182,10 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>10</v>
@@ -16214,10 +16208,10 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>10</v>
@@ -16240,10 +16234,10 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>10</v>
@@ -16266,10 +16260,10 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>10</v>
@@ -16292,10 +16286,10 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" s="12" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="B467" s="12" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="C467" s="12" t="s">
         <v>10</v>
@@ -16318,10 +16312,10 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="2" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>10</v>
@@ -16344,10 +16338,10 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>10</v>
@@ -16370,10 +16364,10 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" s="4" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>10</v>
@@ -16396,10 +16390,10 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" s="6" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="B471" s="6" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="C471" s="6" t="s">
         <v>10</v>
@@ -16422,10 +16416,10 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="4" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>10</v>
@@ -16448,10 +16442,10 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="4" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>10</v>
@@ -16474,10 +16468,10 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="8" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="B474" s="8" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C474" s="8" t="s">
         <v>10</v>
@@ -16500,13 +16494,13 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="12" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="B475" s="12" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="C475" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D475" s="13">
         <v>0</v>
@@ -16526,10 +16520,10 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="6" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="B476" s="6" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="C476" s="6" t="s">
         <v>10</v>
@@ -16552,10 +16546,10 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="10" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="B477" s="10" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="C477" s="10" t="s">
         <v>10</v>
@@ -16578,10 +16572,10 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" s="10" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="B478" s="10" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="C478" s="10" t="s">
         <v>10</v>
@@ -16604,10 +16598,10 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" s="4" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>10</v>
@@ -16630,10 +16624,10 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" s="10" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="B480" s="10" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
       <c r="C480" s="10" t="s">
         <v>10</v>
@@ -16656,10 +16650,10 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" s="6" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="B481" s="6" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="C481" s="6" t="s">
         <v>10</v>
@@ -16682,10 +16676,10 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>10</v>
@@ -16708,10 +16702,10 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" s="4" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>10</v>
@@ -16734,10 +16728,10 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" s="8" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="B484" s="8" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="C484" s="8" t="s">
         <v>10</v>
@@ -16760,10 +16754,10 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" s="10" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="B485" s="10" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="C485" s="10" t="s">
         <v>10</v>
@@ -16786,10 +16780,10 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" s="10" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="B486" s="10" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="C486" s="10" t="s">
         <v>10</v>
@@ -16812,10 +16806,10 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>10</v>
@@ -16838,10 +16832,10 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" s="4" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>10</v>
@@ -16864,10 +16858,10 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" s="4" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>10</v>
@@ -16890,10 +16884,10 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A490" s="12" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="B490" s="12" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="C490" s="12" t="s">
         <v>10</v>
@@ -16916,10 +16910,10 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" s="6" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="B491" s="6" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="C491" s="6" t="s">
         <v>10</v>
@@ -16942,10 +16936,10 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>10</v>
@@ -16968,10 +16962,10 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" s="12" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B493" s="12" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="C493" s="12" t="s">
         <v>10</v>
@@ -16994,10 +16988,10 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" s="10" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="B494" s="10" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="C494" s="10" t="s">
         <v>10</v>
@@ -17020,10 +17014,10 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" s="12" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="B495" s="12" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="C495" s="12" t="s">
         <v>10</v>
@@ -17046,10 +17040,10 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" s="10" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="B496" s="10" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="C496" s="10" t="s">
         <v>10</v>
@@ -17072,10 +17066,10 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" s="12" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="B497" s="12" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="C497" s="12" t="s">
         <v>10</v>
@@ -17098,10 +17092,10 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" s="12" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="B498" s="12" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="C498" s="12" t="s">
         <v>10</v>
@@ -17124,10 +17118,10 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A499" s="4" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="C499" s="4" t="s">
         <v>10</v>
@@ -17150,10 +17144,10 @@
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A500" s="12" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c r="B500" s="12" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="C500" s="12" t="s">
         <v>10</v>
@@ -17176,10 +17170,10 @@
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>10</v>
@@ -17202,10 +17196,10 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A502" s="12" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="B502" s="12" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="C502" s="12" t="s">
         <v>10</v>
@@ -17228,10 +17222,10 @@
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A503" s="10" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="B503" s="10" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="C503" s="10" t="s">
         <v>10</v>
@@ -17254,10 +17248,10 @@
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A504" s="4" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>982</v>
+        <v>970</v>
       </c>
       <c r="C504" s="4" t="s">
         <v>10</v>
@@ -17280,10 +17274,10 @@
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>10</v>
@@ -17306,10 +17300,10 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A506" s="6" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="B506" s="6" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="C506" s="6" t="s">
         <v>10</v>
@@ -17332,10 +17326,10 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A507" s="4" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="C507" s="4" t="s">
         <v>10</v>
@@ -17358,10 +17352,10 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A508" s="12" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="B508" s="12" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="C508" s="12" t="s">
         <v>10</v>
@@ -17384,10 +17378,10 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A509" s="10" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="B509" s="10" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="C509" s="10" t="s">
         <v>10</v>
@@ -17410,10 +17404,10 @@
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A510" s="10" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="B510" s="10" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
       <c r="C510" s="10" t="s">
         <v>10</v>
@@ -17436,10 +17430,10 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A511" s="8" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="B511" s="8" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="C511" s="8" t="s">
         <v>10</v>
@@ -17462,10 +17456,10 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A512" s="12" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="B512" s="12" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C512" s="12" t="s">
         <v>10</v>
@@ -17488,10 +17482,10 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>10</v>
@@ -17514,10 +17508,10 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A514" s="4" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="C514" s="4" t="s">
         <v>10</v>
@@ -17540,10 +17534,10 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A515" s="10" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="B515" s="10" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="C515" s="10" t="s">
         <v>10</v>
@@ -17566,10 +17560,10 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A516" s="10" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="B516" s="10" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="C516" s="10" t="s">
         <v>10</v>
@@ -17592,10 +17586,10 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A517" s="12" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="B517" s="12" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="C517" s="12" t="s">
         <v>10</v>
@@ -17618,10 +17612,10 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" s="6" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="B518" s="6" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="C518" s="6" t="s">
         <v>10</v>
@@ -17644,10 +17638,10 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" s="10" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="B519" s="10" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="C519" s="10" t="s">
         <v>10</v>
@@ -17670,10 +17664,10 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" s="4" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="C520" s="4" t="s">
         <v>10</v>
@@ -17696,10 +17690,10 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" s="10" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="B521" s="10" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="C521" s="10" t="s">
         <v>10</v>
@@ -17722,10 +17716,10 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" s="10" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="B522" s="10" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="C522" s="10" t="s">
         <v>10</v>
@@ -17748,10 +17742,10 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" s="10" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="B523" s="10" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="C523" s="10" t="s">
         <v>10</v>
@@ -17774,10 +17768,10 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" s="4" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>10</v>
@@ -17800,10 +17794,10 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" s="4" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="C525" s="4" t="s">
         <v>10</v>
@@ -17826,10 +17820,10 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" s="2" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>10</v>
@@ -17852,10 +17846,10 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>10</v>
@@ -17878,13 +17872,13 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D528" s="3">
         <v>1</v>
@@ -17904,10 +17898,10 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>10</v>
@@ -17930,10 +17924,10 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>10</v>
@@ -17956,10 +17950,10 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" s="4" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="C531" s="4" t="s">
         <v>10</v>
@@ -17982,10 +17976,10 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" s="4" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="B532" s="4" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="C532" s="4" t="s">
         <v>10</v>
@@ -18008,10 +18002,10 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" s="4" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="C533" s="4" t="s">
         <v>10</v>
@@ -18034,10 +18028,10 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" s="6" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="B534" s="6" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="C534" s="6" t="s">
         <v>10</v>
@@ -18060,10 +18054,10 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>10</v>
@@ -18086,10 +18080,10 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" s="10" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="B536" s="10" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="C536" s="10" t="s">
         <v>10</v>
@@ -18112,10 +18106,10 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" s="10" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="B537" s="10" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="C537" s="10" t="s">
         <v>10</v>
@@ -18138,10 +18132,10 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" s="10" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="B538" s="10" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="C538" s="10" t="s">
         <v>10</v>
@@ -18164,10 +18158,10 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" s="12" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="B539" s="12" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="C539" s="12" t="s">
         <v>10</v>
@@ -18190,10 +18184,10 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" s="2" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>10</v>
@@ -18216,10 +18210,10 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" s="10" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="B541" s="10" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="C541" s="10" t="s">
         <v>10</v>
@@ -18242,10 +18236,10 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A542" s="10" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="B542" s="10" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="C542" s="10" t="s">
         <v>10</v>
@@ -18268,10 +18262,10 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A543" s="8" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="B543" s="8" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="C543" s="8" t="s">
         <v>10</v>
@@ -18294,10 +18288,10 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A544" s="10" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="B544" s="10" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="C544" s="10" t="s">
         <v>10</v>
@@ -18320,13 +18314,13 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A545" s="4" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="C545" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D545" s="5">
         <v>0</v>
@@ -18346,10 +18340,10 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A546" s="4" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="C546" s="4" t="s">
         <v>10</v>
@@ -18372,13 +18366,13 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" s="4" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="C547" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D547" s="5">
         <v>0</v>
@@ -18398,10 +18392,10 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>10</v>
@@ -18424,10 +18418,10 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" s="6" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="B549" s="6" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="C549" s="6" t="s">
         <v>10</v>
@@ -18450,10 +18444,10 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" s="6" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="B550" s="6" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="C550" s="6" t="s">
         <v>10</v>
@@ -18476,13 +18470,13 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" s="8" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="B551" s="8" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="C551" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D551" s="9">
         <v>0</v>
@@ -18502,13 +18496,13 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" s="8" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="B552" s="8" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="C552" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D552" s="9">
         <v>0</v>
@@ -18528,13 +18522,13 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A553" s="10" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="B553" s="10" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D553" s="11">
         <v>0</v>
@@ -18554,10 +18548,10 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A554" s="8" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="B554" s="8" t="s">
-        <v>1076</v>
+        <v>1064</v>
       </c>
       <c r="C554" s="8" t="s">
         <v>10</v>
@@ -18580,10 +18574,10 @@
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A555" s="8" t="s">
-        <v>1077</v>
+        <v>1065</v>
       </c>
       <c r="B555" s="8" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="C555" s="8" t="s">
         <v>10</v>
@@ -18606,10 +18600,10 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" s="10" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="B556" s="10" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="C556" s="10" t="s">
         <v>10</v>
@@ -18632,10 +18626,10 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" s="10" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="B557" s="10" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="C557" s="10" t="s">
         <v>10</v>
@@ -18658,10 +18652,10 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" s="10" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="B558" s="10" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="C558" s="10" t="s">
         <v>10</v>
@@ -18684,10 +18678,10 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" s="4" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B559" s="4" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C559" s="4" t="s">
         <v>10</v>
@@ -18710,10 +18704,10 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A560" s="4" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="B560" s="4" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="C560" s="4" t="s">
         <v>10</v>
@@ -18736,10 +18730,10 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A561" s="8" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="B561" s="8" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="C561" s="8" t="s">
         <v>10</v>
@@ -18762,10 +18756,10 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A562" s="10" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="B562" s="10" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="C562" s="10" t="s">
         <v>10</v>
@@ -18788,10 +18782,10 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A563" s="12" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="B563" s="12" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="C563" s="12" t="s">
         <v>10</v>
@@ -18814,10 +18808,10 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A564" s="12" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="B564" s="12" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="C564" s="12" t="s">
         <v>10</v>
@@ -18840,10 +18834,10 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A565" s="2" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>10</v>
@@ -18866,10 +18860,10 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A566" s="4" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="B566" s="4" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="C566" s="4" t="s">
         <v>10</v>
@@ -18892,10 +18886,10 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A567" s="2" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>10</v>
@@ -18918,10 +18912,10 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>10</v>
@@ -18944,10 +18938,10 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A569" s="6" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="B569" s="6" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="C569" s="6" t="s">
         <v>10</v>
@@ -18970,10 +18964,10 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>10</v>
@@ -18996,10 +18990,10 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A571" s="2" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>10</v>
@@ -19022,10 +19016,10 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A572" s="2" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>10</v>
@@ -19048,10 +19042,10 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A573" s="10" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="B573" s="10" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="C573" s="10" t="s">
         <v>10</v>
@@ -19074,10 +19068,10 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A574" s="2" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>10</v>
@@ -19100,10 +19094,10 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A575" s="2" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>10</v>
@@ -19126,10 +19120,10 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A576" s="12" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="B576" s="12" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="C576" s="12" t="s">
         <v>10</v>
@@ -19152,10 +19146,10 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A577" s="4" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="C577" s="4" t="s">
         <v>10</v>
@@ -19178,10 +19172,10 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A578" s="6" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
       <c r="B578" s="6" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="C578" s="6" t="s">
         <v>10</v>
@@ -19204,13 +19198,13 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A579" s="8" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="B579" s="8" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="C579" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D579" s="9">
         <v>0</v>
@@ -19230,10 +19224,10 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A580" s="10" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="C580" s="10" t="s">
         <v>10</v>
@@ -19256,10 +19250,10 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A581" s="10" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="B581" s="10" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="C581" s="10" t="s">
         <v>10</v>
@@ -19282,10 +19276,10 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A582" s="2" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>10</v>
@@ -19308,10 +19302,10 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A583" s="6" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="B583" s="6" t="s">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="C583" s="6" t="s">
         <v>10</v>
@@ -19334,10 +19328,10 @@
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A584" s="10" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="B584" s="10" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="C584" s="10" t="s">
         <v>10</v>
@@ -19360,10 +19354,10 @@
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A585" s="10" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="B585" s="10" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="C585" s="10" t="s">
         <v>10</v>
@@ -19386,10 +19380,10 @@
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A586" s="2" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>10</v>
@@ -19412,10 +19406,10 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>10</v>
@@ -19438,13 +19432,13 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A588" s="2" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D588" s="3">
         <v>1</v>
@@ -19464,10 +19458,10 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A589" s="4" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="B589" s="4" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
       <c r="C589" s="4" t="s">
         <v>10</v>
@@ -19490,10 +19484,10 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A590" s="10" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="B590" s="10" t="s">
-        <v>1146</v>
+        <v>1134</v>
       </c>
       <c r="C590" s="10" t="s">
         <v>10</v>
@@ -19516,10 +19510,10 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A591" s="4" t="s">
-        <v>1147</v>
+        <v>1135</v>
       </c>
       <c r="B591" s="4" t="s">
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="C591" s="4" t="s">
         <v>10</v>
@@ -19542,10 +19536,10 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A592" s="12" t="s">
-        <v>1149</v>
+        <v>1137</v>
       </c>
       <c r="B592" s="12" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="C592" s="12" t="s">
         <v>10</v>
@@ -19568,10 +19562,10 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A593" s="4" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="B593" s="4" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="C593" s="4" t="s">
         <v>10</v>
@@ -19594,10 +19588,10 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A594" s="10" t="s">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="B594" s="10" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="C594" s="10" t="s">
         <v>10</v>
@@ -19620,10 +19614,10 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1156</v>
+        <v>1144</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>10</v>
@@ -19646,10 +19640,10 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A596" s="2" t="s">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1158</v>
+        <v>1146</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>10</v>
@@ -19672,10 +19666,10 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A597" s="10" t="s">
-        <v>1159</v>
+        <v>1147</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="C597" s="10" t="s">
         <v>10</v>
@@ -19698,10 +19692,10 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A598" s="10" t="s">
-        <v>1161</v>
+        <v>1149</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="C598" s="10" t="s">
         <v>10</v>
@@ -19724,10 +19718,10 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A599" s="4" t="s">
-        <v>1163</v>
+        <v>1151</v>
       </c>
       <c r="B599" s="4" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="C599" s="4" t="s">
         <v>10</v>
@@ -19750,10 +19744,10 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A600" s="12" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
       <c r="B600" s="12" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="C600" s="12" t="s">
         <v>10</v>
@@ -19776,10 +19770,10 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A601" s="4" t="s">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="B601" s="4" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="C601" s="4" t="s">
         <v>10</v>
@@ -19802,10 +19796,10 @@
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A602" s="4" t="s">
-        <v>1169</v>
+        <v>1157</v>
       </c>
       <c r="B602" s="4" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="C602" s="4" t="s">
         <v>10</v>
@@ -19828,10 +19822,10 @@
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A603" s="12" t="s">
-        <v>1171</v>
+        <v>1159</v>
       </c>
       <c r="B603" s="12" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
       <c r="C603" s="12" t="s">
         <v>10</v>
@@ -19854,10 +19848,10 @@
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A604" s="12" t="s">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="B604" s="12" t="s">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="C604" s="12" t="s">
         <v>10</v>
@@ -19880,10 +19874,10 @@
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A605" s="12" t="s">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="B605" s="12" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="C605" s="12" t="s">
         <v>10</v>
@@ -19906,10 +19900,10 @@
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A606" s="12" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="B606" s="12" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="C606" s="12" t="s">
         <v>10</v>
@@ -19932,13 +19926,13 @@
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A607" s="6" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="B607" s="6" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="C607" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D607" s="7">
         <v>1</v>
@@ -19958,13 +19952,13 @@
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A608" s="6" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="B608" s="6" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="C608" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D608" s="7">
         <v>1</v>
@@ -19984,13 +19978,13 @@
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D609" s="3">
         <v>1</v>
@@ -20010,10 +20004,10 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A610" s="4" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
       <c r="B610" s="4" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="C610" s="4" t="s">
         <v>10</v>
@@ -20036,10 +20030,10 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A611" s="10" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="B611" s="10" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
       <c r="C611" s="10" t="s">
         <v>10</v>
@@ -20062,10 +20056,10 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A612" s="10" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="B612" s="10" t="s">
-        <v>1187</v>
+        <v>1175</v>
       </c>
       <c r="C612" s="10" t="s">
         <v>10</v>
@@ -20088,10 +20082,10 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A613" s="2" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>10</v>
@@ -20114,10 +20108,10 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A614" s="4" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="B614" s="4" t="s">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="C614" s="4" t="s">
         <v>10</v>
@@ -20140,10 +20134,10 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A615" s="4" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="B615" s="4" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="C615" s="4" t="s">
         <v>10</v>
@@ -20166,10 +20160,10 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A616" s="4" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="B616" s="4" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="C616" s="4" t="s">
         <v>10</v>
@@ -20192,13 +20186,13 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A617" s="8" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="B617" s="8" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="C617" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D617" s="9">
         <v>0</v>
@@ -20218,10 +20212,10 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>10</v>
@@ -20244,10 +20238,10 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A619" s="6" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="B619" s="6" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
       <c r="C619" s="6" t="s">
         <v>10</v>
@@ -20270,13 +20264,13 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A620" s="10" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="B620" s="10" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D620" s="11">
         <v>0</v>
@@ -20296,10 +20290,10 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A621" s="10" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
       <c r="B621" s="10" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="C621" s="10" t="s">
         <v>10</v>
@@ -20322,10 +20316,10 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
-        <v>1204</v>
+        <v>1192</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1205</v>
+        <v>1193</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>10</v>
@@ -20348,10 +20342,10 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A623" s="8" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="B623" s="8" t="s">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="C623" s="8" t="s">
         <v>10</v>
@@ -20374,10 +20368,10 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A624" s="10" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>1209</v>
+        <v>1197</v>
       </c>
       <c r="C624" s="10" t="s">
         <v>10</v>
@@ -20400,10 +20394,10 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A625" s="8" t="s">
-        <v>1210</v>
+        <v>1198</v>
       </c>
       <c r="B625" s="8" t="s">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="C625" s="8" t="s">
         <v>10</v>
@@ -20426,10 +20420,10 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A626" s="4" t="s">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="B626" s="4" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
       <c r="C626" s="4" t="s">
         <v>10</v>
@@ -20452,10 +20446,10 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A627" s="4" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
       <c r="B627" s="4" t="s">
-        <v>1215</v>
+        <v>1203</v>
       </c>
       <c r="C627" s="4" t="s">
         <v>10</v>
@@ -20478,10 +20472,10 @@
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A628" s="2" t="s">
-        <v>1216</v>
+        <v>1204</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>10</v>
@@ -20504,10 +20498,10 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A629" s="10" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>1219</v>
+        <v>1207</v>
       </c>
       <c r="C629" s="10" t="s">
         <v>10</v>
@@ -20531,6 +20525,7 @@
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -20546,13 +20541,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="B1" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="C1" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -20560,10 +20555,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -20571,10 +20566,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -20582,10 +20577,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -20593,10 +20588,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -20604,10 +20599,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
     </row>
   </sheetData>
